--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260609.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>65,293,697</t>
+          <t>103,103,563</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>103,103,563</t>
+          <t>65,293,697</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>227,064,132</t>
+          <t>1,762,819</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,762,819</t>
+          <t>1,660,462</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,660,462</t>
+          <t>227,064,132</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>87,792,716</t>
+          <t>37,117,217</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>37,117,217</t>
+          <t>87,792,716</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202606NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>20,195,607</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202606NYF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>20,195,607</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
